--- a/LLM系統開發甘特圖_v4_7.xlsx
+++ b/LLM系統開發甘特圖_v4_7.xlsx
@@ -1808,10 +1808,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="2" max="2" width="47.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="12.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="9.85714285714286" customWidth="1"/>
-    <col min="5" max="17" width="6" customWidth="1"/>
+    <col min="5" max="5" width="19.2857142857143" customWidth="1"/>
+    <col min="6" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
@@ -2142,7 +2143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" spans="1:17">
+    <row r="9" ht="17" customHeight="1" spans="1:17">
       <c r="A9" s="20" t="s">
         <v>44</v>
       </c>
@@ -2619,7 +2620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1" spans="1:17">
+    <row r="18" ht="24" customHeight="1" spans="1:17">
       <c r="A18" s="32" t="s">
         <v>62</v>
       </c>
@@ -2778,7 +2779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1" spans="1:17">
+    <row r="21" spans="1:17">
       <c r="A21" s="37" t="s">
         <v>68</v>
       </c>
@@ -2990,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1" spans="1:17">
+    <row r="25" ht="17" customHeight="1" spans="1:17">
       <c r="A25" s="42" t="s">
         <v>77</v>
       </c>
@@ -3202,7 +3203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1" spans="1:17">
+    <row r="29" ht="16" customHeight="1" spans="1:17">
       <c r="A29" s="46" t="s">
         <v>82</v>
       </c>
@@ -3255,7 +3256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" spans="1:17">
+    <row r="30" spans="1:17">
       <c r="A30" s="12" t="s">
         <v>2</v>
       </c>
